--- a/data/trans_orig/P37A$vacunaempresa-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P37A$vacunaempresa-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14419</t>
+          <t>14132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22710</t>
+          <t>21880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>459357</t>
+          <t>459644</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470150</t>
+          <t>469986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294483</t>
+          <t>294037</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>757747</t>
+          <t>758577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>772488</t>
+          <t>772712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6686</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24071</t>
+          <t>22587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>6711</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>8060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>25149</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>342863</t>
+          <t>344347</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>360248</t>
+          <t>360400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>364001</t>
+          <t>365154</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713708</t>
+          <t>713650</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>731191</t>
+          <t>730739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>8058</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>814</t>
+          <t>813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534942</t>
+          <t>534331</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>541573</t>
+          <t>541586</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>702634</t>
+          <t>701848</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>709357</t>
+          <t>709358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>18746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26587</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1220796</t>
+          <t>1219588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1233110</t>
+          <t>1232702</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>701043</t>
+          <t>701046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>711434</t>
+          <t>712049</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1926033</t>
+          <t>1926524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1942614</t>
+          <t>1942771</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8742</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345740</t>
+          <t>345476</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>560942</t>
+          <t>560023</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>910565</t>
+          <t>909794</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1242925</t>
+          <t>1242924</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1541840</t>
+          <t>1542466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25138</t>
+          <t>24915</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49833</t>
+          <t>48056</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28010</t>
+          <t>27504</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40169</t>
+          <t>40305</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67491</t>
+          <t>70267</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3220357</t>
+          <t>3222134</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3245052</t>
+          <t>3245275</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3350114</t>
+          <t>3350620</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3367140</t>
+          <t>3367041</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6580823</t>
+          <t>6578047</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6608145</t>
+          <t>6608009</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>28217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17505</t>
+          <t>17530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16749</t>
+          <t>17295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38848</t>
+          <t>38451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409462</t>
+          <t>408994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427367</t>
+          <t>426659</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296949</t>
+          <t>296924</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310469</t>
+          <t>309744</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712817</t>
+          <t>713214</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>734916</t>
+          <t>734370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26571</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>10725</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31721</t>
+          <t>31323</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>392226</t>
+          <t>392588</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>410705</t>
+          <t>410964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>324808</t>
+          <t>325015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336906</t>
+          <t>336877</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>725087</t>
+          <t>725485</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>746361</t>
+          <t>746083</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>622821</t>
+          <t>623557</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>882933</t>
+          <t>882957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14089</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>6939</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23925</t>
+          <t>23995</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11032</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30572</t>
+          <t>31817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1144920</t>
+          <t>1144872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1156877</t>
+          <t>1156934</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>742732</t>
+          <t>742662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>759817</t>
+          <t>759718</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1895095</t>
+          <t>1893850</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1914635</t>
+          <t>1914026</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>10100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16142</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>500251</t>
+          <t>500156</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508749</t>
+          <t>508763</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>752267</t>
+          <t>751422</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>760561</t>
+          <t>760577</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1255976</t>
+          <t>1256998</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1267492</t>
+          <t>1268275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261555</t>
+          <t>260288</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1369067</t>
+          <t>1368767</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33979</t>
+          <t>33941</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63999</t>
+          <t>64467</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21252</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45333</t>
+          <t>43212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59482</t>
+          <t>60057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97385</t>
+          <t>97276</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3357911</t>
+          <t>3357443</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3387931</t>
+          <t>3387969</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3504792</t>
+          <t>3506913</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3528873</t>
+          <t>3530804</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6874650</t>
+          <t>6874759</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6912553</t>
+          <t>6911978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23241</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>416240</t>
+          <t>415744</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427058</t>
+          <t>427140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>332913</t>
+          <t>331910</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>343480</t>
+          <t>343292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>752906</t>
+          <t>753559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>768508</t>
+          <t>768606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1854</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10509</t>
+          <t>10617</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>368209</t>
+          <t>367318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376208</t>
+          <t>376217</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>367815</t>
+          <t>367794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738991</t>
+          <t>738883</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747646</t>
+          <t>747634</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5659</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516255</t>
+          <t>517086</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>682335</t>
+          <t>682427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19315</t>
+          <t>19169</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7436</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>23658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1140565</t>
+          <t>1141479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>806561</t>
+          <t>806707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>820708</t>
+          <t>821019</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1952641</t>
+          <t>1951856</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1968078</t>
+          <t>1968388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7395,7 +7395,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>8843</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>611848</t>
+          <t>610506</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -7558,7 +7558,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1349543</t>
+          <t>1350107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8899</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25777</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11197</t>
+          <t>10969</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23659</t>
+          <t>24962</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>49770</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3359945</t>
+          <t>3359309</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3376823</t>
+          <t>3377385</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3502173</t>
+          <t>3502335</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3520399</t>
+          <t>3520627</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6867548</t>
+          <t>6868377</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6893659</t>
+          <t>6892356</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>32414</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41473</t>
+          <t>45540</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>36792</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26217</t>
+          <t>27066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47599</t>
+          <t>49359</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>66345</t>
+          <t>69206</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52199</t>
+          <t>56186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82333</t>
+          <t>85697</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>474869</t>
+          <t>518204</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>463739</t>
+          <t>505078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>485292</t>
+          <t>527625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>411465</t>
+          <t>451619</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399868</t>
+          <t>439052</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>421250</t>
+          <t>461345</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>886334</t>
+          <t>969823</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870346</t>
+          <t>953332</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>900480</t>
+          <t>982843</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,59%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26906</t>
+          <t>28494</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17326</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>40658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21025</t>
+          <t>22686</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>40680</t>
+          <t>42974</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30028</t>
+          <t>32427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54670</t>
+          <t>57961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>425307</t>
+          <t>454718</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415093</t>
+          <t>442554</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>434887</t>
+          <t>465016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>368807</t>
+          <t>408663</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361555</t>
+          <t>400457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373611</t>
+          <t>413865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>794113</t>
+          <t>863381</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>780123</t>
+          <t>848394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>804765</t>
+          <t>873928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,42%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>7227</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>15113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>15802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>661327</t>
+          <t>464385</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>651460</t>
+          <t>456499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666712</t>
+          <t>468307</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,27 +9467,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>165607</t>
+          <t>186054</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162848</t>
+          <t>182680</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>826933</t>
+          <t>650439</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>819133</t>
+          <t>643307</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>833332</t>
+          <t>655108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>28924</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48223</t>
+          <t>49306</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25673</t>
+          <t>38794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68017</t>
+          <t>64020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>64420</t>
+          <t>66155</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42057</t>
+          <t>52395</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82588</t>
+          <t>82790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1018622</t>
+          <t>1114994</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1008555</t>
+          <t>1102919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1026219</t>
+          <t>1121795</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>929871</t>
+          <t>811905</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>910077</t>
+          <t>797191</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>952421</t>
+          <t>822417</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1948492</t>
+          <t>1926899</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1930324</t>
+          <t>1910264</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1970855</t>
+          <t>1940659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>14014</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>21738</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>471266</t>
+          <t>562980</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>464972</t>
+          <t>556295</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474030</t>
+          <t>566479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>833125</t>
+          <t>821820</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>826753</t>
+          <t>816363</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>836745</t>
+          <t>825480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1304392</t>
+          <t>1384800</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1296847</t>
+          <t>1377076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1309150</t>
+          <t>1390251</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>15623</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>551</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22412</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -10461,27 +10461,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>235271</t>
+          <t>233125</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>223118</t>
+          <t>221605</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>758280</t>
+          <t>841030</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>752330</t>
+          <t>833819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>760895</t>
+          <t>843730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>993551</t>
+          <t>1074155</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>979466</t>
+          <t>1063936</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>999310</t>
+          <t>1079284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>89399</t>
+          <t>94072</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67438</t>
+          <t>76262</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>111927</t>
+          <t>115361</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>110604</t>
+          <t>114301</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>87360</t>
+          <t>97662</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132707</t>
+          <t>134677</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>200003</t>
+          <t>208373</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>165673</t>
+          <t>182011</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>232721</t>
+          <t>240377</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3286661</t>
+          <t>3348404</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3264133</t>
+          <t>3327115</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3308622</t>
+          <t>3366214</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3467154</t>
+          <t>3521092</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3445051</t>
+          <t>3500716</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3490398</t>
+          <t>3537731</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6753815</t>
+          <t>6869496</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6721097</t>
+          <t>6837492</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6788145</t>
+          <t>6895858</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
